--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1462,7 +1462,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/EncounterInicioLE)
 </t>
   </si>
   <si>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4067" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -570,6 +570,26 @@
   </si>
   <si>
     <t>Doc Acreditacion Cuidador</t>
+  </si>
+  <si>
+    <t>EspecialidadMedicaDestinoCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/EspecialidadMedicaDestinoCodigo}
+</t>
+  </si>
+  <si>
+    <t>Especialidad Médica Destino Código</t>
+  </si>
+  <si>
+    <t>SubEspecialidadMedicaDestinoCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/SubEspecialidadMedicaDestinoCodigo}
+</t>
+  </si>
+  <si>
+    <t>SubEspecialidad Médica Destino Código</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -1947,24 +1967,39 @@
     <t>paciente</t>
   </si>
   <si>
-    <t>QuestionnaireResponse</t>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PacienteLE)
+</t>
+  </si>
+  <si>
+    <t>Anamnesis</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/QuestionnaireResponseInicioLE)
 </t>
   </si>
   <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/CondicionInicio1LE)
+    <t>DiagnosticoSospecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioDiagnosticoSospechaLE)
 </t>
   </si>
   <si>
-    <t>AllergyIntolerance</t>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioSospechaGesLE)
+</t>
+  </si>
+  <si>
+    <t>TipoAlergia</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/AllergyIntoleranceInicioLE)
+</t>
+  </si>
+  <si>
+    <t>IndiceComorbilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioIndiceComorbilidadLE)
 </t>
   </si>
   <si>
@@ -2382,11 +2417,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN112"/>
+  <dimension ref="A1:AN116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.68359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.9296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -4821,45 +4856,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4907,7 +4940,7 @@
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>76</v>
@@ -4916,7 +4949,7 @@
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>136</v>
@@ -4928,7 +4961,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4937,20 +4970,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B23" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="C23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>184</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>86</v>
@@ -4959,20 +4994,18 @@
         <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>78</v>
@@ -5009,19 +5042,19 @@
         <v>78</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AC23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -5030,66 +5063,66 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5137,7 +5170,7 @@
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5149,27 +5182,27 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -5177,30 +5210,32 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>78</v>
@@ -5237,83 +5272,85 @@
         <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AC25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AF25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL25" t="s" s="2">
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
@@ -5351,19 +5388,19 @@
         <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
@@ -5375,27 +5412,27 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5412,26 +5449,22 @@
         <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5455,13 +5488,13 @@
         <v>78</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>78</v>
@@ -5479,7 +5512,7 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
@@ -5491,16 +5524,16 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5509,45 +5542,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5571,52 +5602,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5627,7 +5658,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5644,22 +5675,26 @@
         <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5683,13 +5718,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5707,7 +5742,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5719,16 +5754,16 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5737,43 +5772,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5797,52 +5834,52 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5851,9 +5888,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5861,35 +5898,31 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5937,28 +5970,28 @@
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5969,18 +6002,18 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
@@ -5992,15 +6025,17 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M32" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>78</v>
@@ -6037,31 +6072,31 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
@@ -6070,7 +6105,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6079,43 +6114,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6151,19 +6188,19 @@
         <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
@@ -6175,16 +6212,16 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6193,9 +6230,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -6203,35 +6240,31 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6279,7 +6312,7 @@
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
@@ -6291,16 +6324,16 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6311,18 +6344,18 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>78</v>
@@ -6331,19 +6364,19 @@
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -6381,40 +6414,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6425,7 +6458,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6448,17 +6481,19 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M36" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="N36" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
@@ -6468,7 +6503,7 @@
         <v>78</v>
       </c>
       <c r="R36" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>78</v>
@@ -6507,7 +6542,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6525,10 +6560,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6537,9 +6572,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6553,7 +6588,7 @@
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6562,18 +6597,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M37" s="2"/>
-      <c r="N37" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6621,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6639,10 +6674,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6651,9 +6686,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6661,13 +6696,13 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6676,19 +6711,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6698,7 +6731,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6737,7 +6770,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6755,10 +6788,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6767,9 +6800,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6783,7 +6816,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6792,19 +6825,17 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6853,7 +6884,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6871,10 +6902,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6885,7 +6916,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6908,19 +6939,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>99</v>
+        <v>278</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6933,7 +6964,7 @@
         <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>293</v>
+        <v>78</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>78</v>
@@ -6969,7 +7000,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6987,10 +7018,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6999,9 +7030,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -7009,13 +7040,13 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -7024,18 +7055,20 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7047,7 +7080,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>301</v>
+        <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7083,7 +7116,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7101,10 +7134,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7115,7 +7148,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7138,16 +7171,20 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>306</v>
+        <v>99</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7159,7 +7196,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7195,7 +7232,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7213,10 +7250,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7225,9 +7262,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7235,13 +7272,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7250,16 +7287,16 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -7273,7 +7310,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7309,7 +7346,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7327,10 +7364,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7341,7 +7378,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7352,7 +7389,7 @@
         <v>76</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>78</v>
@@ -7364,17 +7401,15 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7423,13 +7458,13 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>78</v>
@@ -7438,13 +7473,13 @@
         <v>97</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7455,7 +7490,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7466,7 +7501,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7478,16 +7513,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>99</v>
+        <v>319</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7537,13 +7572,13 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7552,13 +7587,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7569,11 +7604,11 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7592,15 +7627,17 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M46" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
         <v>78</v>
@@ -7649,7 +7686,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7664,13 +7701,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7681,11 +7718,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7704,15 +7741,17 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>343</v>
+        <v>99</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M47" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7761,7 +7800,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7776,13 +7815,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7793,18 +7832,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>78</v>
@@ -7816,20 +7855,16 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>185</v>
+        <v>341</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7877,13 +7912,13 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>78</v>
@@ -7892,13 +7927,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7907,42 +7942,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>78</v>
@@ -7967,13 +8000,13 @@
         <v>78</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>78</v>
@@ -7991,13 +8024,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -8006,58 +8039,60 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>367</v>
+        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>368</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8081,13 +8116,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8105,10 +8140,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8120,16 +8155,16 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>128</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>377</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -8137,7 +8172,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8145,7 +8180,7 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>85</v>
@@ -8154,26 +8189,24 @@
         <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>219</v>
+        <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8197,13 +8230,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>383</v>
+        <v>219</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8221,13 +8254,13 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>78</v>
@@ -8236,24 +8269,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8261,30 +8294,32 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>199</v>
+        <v>376</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M52" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -8309,13 +8344,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8333,10 +8368,10 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>201</v>
+        <v>375</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -8345,61 +8380,63 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>204</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>205</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8423,31 +8460,31 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>207</v>
+        <v>384</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
@@ -8459,27 +8496,27 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>202</v>
+        <v>393</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8487,35 +8524,31 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8563,28 +8596,28 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8595,18 +8628,18 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>78</v>
@@ -8618,15 +8651,17 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M55" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>78</v>
@@ -8663,31 +8698,31 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
@@ -8696,7 +8731,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8705,43 +8740,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8777,19 +8814,19 @@
         <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
@@ -8801,16 +8838,16 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8819,9 +8856,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8829,35 +8866,31 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8905,7 +8938,7 @@
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8917,16 +8950,16 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8937,18 +8970,18 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>78</v>
@@ -8957,19 +8990,19 @@
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
@@ -9007,40 +9040,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9051,7 +9084,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9074,17 +9107,19 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M59" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="N59" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>78</v>
@@ -9109,11 +9144,13 @@
         <v>78</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="X59" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y59" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>78</v>
@@ -9131,7 +9168,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9149,10 +9186,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9161,9 +9198,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9177,7 +9214,7 @@
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9186,18 +9223,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9245,7 +9282,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9263,10 +9300,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9275,9 +9312,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9285,13 +9322,13 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -9300,19 +9337,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9337,13 +9372,11 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="X61" s="2"/>
       <c r="Y61" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9361,7 +9394,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9379,10 +9412,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9391,9 +9424,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9407,7 +9440,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9416,19 +9449,17 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M62" s="2"/>
       <c r="N62" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9477,7 +9508,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9495,10 +9526,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9507,9 +9538,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9523,7 +9554,7 @@
         <v>85</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9532,22 +9563,24 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>105</v>
+        <v>278</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>401</v>
+        <v>279</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P63" t="s" s="2">
-        <v>403</v>
-      </c>
+      <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9567,13 +9600,13 @@
         <v>78</v>
       </c>
       <c r="W63" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
         <v>78</v>
@@ -9591,7 +9624,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>400</v>
+        <v>283</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9606,24 +9639,24 @@
         <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>407</v>
+        <v>284</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>408</v>
+        <v>285</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9637,35 +9670,33 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>287</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>288</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>289</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>414</v>
+        <v>290</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9709,7 +9740,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>410</v>
+        <v>291</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9724,13 +9755,13 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>416</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>293</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9739,9 +9770,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9755,29 +9786,31 @@
         <v>85</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9797,13 +9830,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9821,7 +9854,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>201</v>
+        <v>406</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9833,27 +9866,27 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9864,32 +9897,38 @@
         <v>76</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>130</v>
+        <v>278</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>131</v>
+        <v>417</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9921,38 +9960,40 @@
         <v>78</v>
       </c>
       <c r="AA66" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD66" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>207</v>
+        <v>416</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9961,13 +10002,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9979,7 +10018,7 @@
         <v>85</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9988,13 +10027,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>423</v>
+        <v>204</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -10051,13 +10090,13 @@
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10077,7 +10116,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -10088,7 +10127,7 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>78</v>
@@ -10100,13 +10139,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>272</v>
+        <v>130</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>425</v>
+        <v>131</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10145,55 +10184,55 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB68" s="2"/>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE68" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AF68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
+      <c r="B69" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10203,26 +10242,24 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>219</v>
+        <v>429</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
         <v>78</v>
@@ -10247,13 +10284,13 @@
         <v>78</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>78</v>
@@ -10271,50 +10308,50 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>428</v>
+        <v>213</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>78</v>
@@ -10323,20 +10360,18 @@
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10361,13 +10396,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10385,43 +10420,43 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10440,18 +10475,18 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M71" s="2"/>
-      <c r="N71" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10475,13 +10510,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10499,7 +10534,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10514,38 +10549,38 @@
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10554,15 +10589,17 @@
         <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>456</v>
+        <v>225</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M72" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>78</v>
@@ -10587,13 +10624,13 @@
         <v>78</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>78</v>
@@ -10611,43 +10648,43 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>463</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10666,16 +10703,18 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10723,7 +10762,7 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>76</v>
@@ -10738,38 +10777,38 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>473</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10778,13 +10817,13 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10835,10 +10874,10 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -10850,28 +10889,28 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>483</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10890,13 +10929,13 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10923,13 +10962,13 @@
         <v>78</v>
       </c>
       <c r="W75" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>488</v>
+        <v>78</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>78</v>
@@ -10947,7 +10986,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10962,28 +11001,28 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10993,7 +11032,7 @@
         <v>85</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -11002,13 +11041,13 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -11059,7 +11098,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11074,28 +11113,28 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11114,17 +11153,15 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>78</v>
@@ -11149,13 +11186,13 @@
         <v>78</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>78</v>
@@ -11173,7 +11210,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11188,28 +11225,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>509</v>
+        <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>511</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11219,7 +11256,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11228,17 +11265,15 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>219</v>
+        <v>500</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11263,13 +11298,13 @@
         <v>78</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>518</v>
+        <v>78</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>78</v>
@@ -11287,7 +11322,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11302,35 +11337,35 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>78</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>78</v>
@@ -11342,16 +11377,16 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -11401,13 +11436,13 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>78</v>
@@ -11416,28 +11451,28 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11447,7 +11482,7 @@
         <v>85</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -11456,15 +11491,17 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M80" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>78</v>
@@ -11489,13 +11526,13 @@
         <v>78</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>78</v>
@@ -11513,13 +11550,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11528,16 +11565,16 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11545,18 +11582,18 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>78</v>
@@ -11565,18 +11602,20 @@
         <v>78</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>198</v>
+        <v>532</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>199</v>
+        <v>533</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M81" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
         <v>78</v>
@@ -11625,72 +11664,70 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>201</v>
+        <v>530</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>202</v>
+        <v>538</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>204</v>
+        <v>540</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>78</v>
@@ -11715,31 +11752,31 @@
         <v>78</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>78</v>
+        <v>542</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>78</v>
+        <v>543</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD82" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>207</v>
+        <v>539</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11751,7 +11788,7 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>78</v>
@@ -11760,18 +11797,18 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>202</v>
+        <v>544</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11779,35 +11816,31 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11831,11 +11864,13 @@
         <v>78</v>
       </c>
       <c r="W83" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="X83" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y83" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
@@ -11853,28 +11888,28 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11885,18 +11920,18 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>78</v>
@@ -11908,15 +11943,17 @@
         <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M84" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
         <v>78</v>
@@ -11953,31 +11990,31 @@
         <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>78</v>
@@ -11986,7 +12023,7 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11995,43 +12032,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12055,31 +12094,29 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="X85" s="2"/>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA85" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD85" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
@@ -12091,16 +12128,16 @@
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12109,9 +12146,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -12119,35 +12156,31 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
       </c>
@@ -12195,7 +12228,7 @@
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12207,16 +12240,16 @@
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12227,18 +12260,18 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>78</v>
@@ -12247,19 +12280,19 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
@@ -12297,40 +12330,40 @@
         <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12341,7 +12374,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12364,17 +12397,19 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M88" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="N88" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>78</v>
@@ -12423,7 +12458,7 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12441,10 +12476,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12453,9 +12488,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12469,7 +12504,7 @@
         <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12478,18 +12513,18 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M89" s="2"/>
-      <c r="N89" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12537,7 +12572,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12555,10 +12590,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12567,9 +12602,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12577,13 +12612,13 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12592,19 +12627,17 @@
         <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="M90" s="2"/>
       <c r="N90" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12653,7 +12686,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12671,10 +12704,10 @@
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12683,9 +12716,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12699,7 +12732,7 @@
         <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12708,19 +12741,17 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M91" s="2"/>
       <c r="N91" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12769,7 +12800,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12787,10 +12818,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12799,9 +12830,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12815,7 +12846,7 @@
         <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12824,16 +12855,20 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>552</v>
+        <v>278</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>534</v>
+        <v>279</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12881,13 +12916,13 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>551</v>
+        <v>283</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>78</v>
@@ -12899,13 +12934,13 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>554</v>
+        <v>285</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12913,7 +12948,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12933,19 +12968,23 @@
         <v>78</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12993,7 +13032,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -13005,16 +13044,16 @@
         <v>78</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -13023,42 +13062,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>130</v>
+        <v>558</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>204</v>
+        <v>540</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>78</v>
@@ -13095,19 +13132,19 @@
         <v>78</v>
       </c>
       <c r="AA94" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD94" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>207</v>
+        <v>557</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13119,7 +13156,7 @@
         <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>78</v>
@@ -13128,18 +13165,18 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>202</v>
+        <v>560</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13147,32 +13184,30 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>558</v>
+        <v>205</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13221,7 +13256,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>561</v>
+        <v>207</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13230,10 +13265,10 @@
         <v>85</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>562</v>
+        <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>78</v>
@@ -13242,7 +13277,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13253,18 +13288,18 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>78</v>
@@ -13273,19 +13308,19 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>564</v>
+        <v>210</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>565</v>
+        <v>211</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>566</v>
+        <v>186</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
@@ -13311,43 +13346,43 @@
         <v>78</v>
       </c>
       <c r="W96" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>567</v>
+        <v>78</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="Z96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>569</v>
+        <v>213</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>78</v>
@@ -13356,7 +13391,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13365,9 +13400,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13375,13 +13410,13 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -13390,16 +13425,16 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13449,7 +13484,7 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13458,7 +13493,7 @@
         <v>85</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>97</v>
@@ -13470,7 +13505,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13481,7 +13516,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13504,16 +13539,16 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13539,13 +13574,13 @@
         <v>78</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>78</v>
+        <v>573</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>78</v>
@@ -13563,7 +13598,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13593,9 +13628,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13609,7 +13644,7 @@
         <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13618,16 +13653,16 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13653,13 +13688,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>584</v>
+        <v>78</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13683,7 +13718,7 @@
         <v>76</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>78</v>
@@ -13692,16 +13727,16 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>586</v>
+        <v>78</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>588</v>
+        <v>199</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13709,7 +13744,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13720,7 +13755,7 @@
         <v>76</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>78</v>
@@ -13732,16 +13767,16 @@
         <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>591</v>
+        <v>204</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13791,13 +13826,13 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>78</v>
@@ -13806,24 +13841,24 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>596</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>597</v>
+        <v>128</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13834,27 +13869,29 @@
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>599</v>
+        <v>225</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="M101" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
         <v>78</v>
@@ -13879,13 +13916,13 @@
         <v>78</v>
       </c>
       <c r="W101" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="Z101" t="s" s="2">
         <v>78</v>
@@ -13903,7 +13940,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13918,16 +13955,16 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13935,11 +13972,11 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13949,25 +13986,25 @@
         <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I102" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J102" t="s" s="2">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -14005,19 +14042,19 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>611</v>
+        <v>78</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14032,40 +14069,38 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="B103" s="2"/>
       <c r="C103" t="s" s="2">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14074,17 +14109,15 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
         <v>78</v>
@@ -14133,7 +14166,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14148,13 +14181,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14163,22 +14196,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="B104" s="2"/>
       <c r="C104" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>86</v>
@@ -14190,16 +14221,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14237,19 +14268,19 @@
         <v>78</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>78</v>
+        <v>617</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
+        <v>618</v>
       </c>
       <c r="AC104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD104" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14264,13 +14295,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14281,13 +14312,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14306,16 +14337,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14365,7 +14396,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14380,13 +14411,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14397,13 +14428,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14422,16 +14453,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14481,7 +14512,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14496,13 +14527,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14513,13 +14544,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14538,16 +14569,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14597,7 +14628,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14612,13 +14643,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14627,41 +14658,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B108" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="C108" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14711,7 +14744,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14726,13 +14759,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14741,45 +14774,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B109" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C109" t="s" s="2">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>219</v>
+        <v>630</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
         <v>78</v>
       </c>
@@ -14803,13 +14836,13 @@
         <v>78</v>
       </c>
       <c r="W109" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>638</v>
+        <v>78</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>639</v>
+        <v>78</v>
       </c>
       <c r="Z109" t="s" s="2">
         <v>78</v>
@@ -14827,7 +14860,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14842,38 +14875,40 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>641</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B110" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="C110" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
@@ -14882,15 +14917,17 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>47</v>
+        <v>614</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="M110" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
         <v>78</v>
@@ -14939,7 +14976,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>642</v>
+        <v>611</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14954,28 +14991,30 @@
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>645</v>
+        <v>619</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>448</v>
+        <v>620</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>647</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="C111" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14985,24 +15024,26 @@
         <v>85</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>198</v>
+        <v>634</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>649</v>
+        <v>614</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M111" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
         <v>78</v>
@@ -15051,13 +15092,13 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>78</v>
@@ -15066,13 +15107,13 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>448</v>
+        <v>620</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -15083,7 +15124,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
@@ -15103,19 +15144,19 @@
         <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
@@ -15165,7 +15206,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15180,23 +15221,477 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M114" s="2"/>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AK112" t="s" s="2">
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B115" s="2"/>
+      <c r="C115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B116" s="2"/>
+      <c r="C116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P116" s="2"/>
+      <c r="Q116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AK116" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AL112" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AL116" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN112">
+  <autoFilter ref="A1:AN116">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15206,7 +15701,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI111">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1967,7 +1967,7 @@
     <t>paciente</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PacienteLE)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$115</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,16 +520,6 @@
   </si>
   <si>
     <t>ExtBool PresentaDiscapacidad</t>
-  </si>
-  <si>
-    <t>PersonaMayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolPersonaMayor}
-</t>
-  </si>
-  <si>
-    <t>ExtBool PersonaMayor</t>
   </si>
   <si>
     <t>OrigenInterconsulta</t>
@@ -2417,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN116"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -4433,7 +4423,7 @@
         <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -4547,7 +4537,7 @@
         <v>169</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -4970,43 +4960,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B23" t="s" s="2">
         <v>179</v>
       </c>
+      <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>181</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="O23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5054,7 +5046,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -5063,7 +5055,7 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>136</v>
@@ -5075,7 +5067,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -5086,43 +5078,41 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J24" t="s" s="2">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5158,19 +5148,19 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5182,29 +5172,31 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="C25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5213,7 +5205,7 @@
         <v>85</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>86</v>
@@ -5225,16 +5217,16 @@
         <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -5272,19 +5264,19 @@
         <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5299,59 +5291,55 @@
         <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -5400,50 +5388,50 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>78</v>
@@ -5455,15 +5443,17 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M27" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
@@ -5500,31 +5490,31 @@
         <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
@@ -5533,7 +5523,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5544,41 +5534,43 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5602,52 +5594,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5656,9 +5648,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5666,34 +5658,34 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5718,13 +5710,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5742,7 +5734,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5760,10 +5752,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5772,9 +5764,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5782,35 +5774,31 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5834,13 +5822,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5858,7 +5846,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5870,16 +5858,16 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5890,18 +5878,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>78</v>
@@ -5913,15 +5901,17 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M31" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
@@ -5958,31 +5948,31 @@
         <v>78</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
@@ -5991,7 +5981,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -6000,43 +5990,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6072,19 +6064,19 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6096,16 +6088,16 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6114,9 +6106,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6124,35 +6116,31 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6200,28 +6188,28 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6232,18 +6220,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>78</v>
@@ -6255,15 +6243,17 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M34" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -6300,31 +6290,31 @@
         <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
@@ -6333,7 +6323,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6342,43 +6332,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6414,40 +6406,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6456,9 +6448,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6466,13 +6458,13 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6481,20 +6473,18 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6542,7 +6532,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6560,10 +6550,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6572,9 +6562,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6582,13 +6572,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6597,18 +6587,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6617,7 +6607,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6656,7 +6646,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6674,10 +6664,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6688,7 +6678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6696,7 +6686,7 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
@@ -6711,17 +6701,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6731,7 +6721,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6770,7 +6760,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6788,10 +6778,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6800,9 +6790,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6816,7 +6806,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6825,17 +6815,19 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M39" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="N39" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6884,7 +6876,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6902,10 +6894,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6916,7 +6908,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6939,19 +6931,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -7000,7 +6992,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -7018,10 +7010,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -7032,7 +7024,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -7055,19 +7047,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -7080,7 +7072,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7116,7 +7108,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7134,10 +7126,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7146,9 +7138,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7156,13 +7148,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7171,20 +7163,18 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7196,7 +7186,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7232,7 +7222,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7250,10 +7240,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7262,9 +7252,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7272,13 +7262,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7287,17 +7277,15 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>78</v>
@@ -7310,7 +7298,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7346,7 +7334,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7364,10 +7352,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7378,7 +7366,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7401,15 +7389,17 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M44" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7458,7 +7448,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7476,10 +7466,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7490,7 +7480,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7501,7 +7491,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7513,16 +7503,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7578,7 +7568,7 @@
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7587,13 +7577,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7604,7 +7594,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7627,16 +7617,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>327</v>
+        <v>99</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7686,7 +7676,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7701,13 +7691,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7718,11 +7708,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7741,17 +7731,15 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7800,7 +7788,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7815,13 +7803,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7832,11 +7820,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7855,13 +7843,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7912,7 +7900,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7927,13 +7915,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7944,18 +7932,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>78</v>
@@ -7967,16 +7955,20 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>349</v>
+        <v>188</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O49" t="s" s="2">
         <v>78</v>
       </c>
@@ -8024,13 +8016,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -8039,13 +8031,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -8054,45 +8046,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8116,13 +8106,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8140,10 +8130,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8155,24 +8145,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8198,13 +8188,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8230,13 +8220,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8254,7 +8244,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8269,24 +8259,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>128</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8294,7 +8284,7 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
@@ -8303,24 +8293,26 @@
         <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8344,13 +8336,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>219</v>
+        <v>386</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8368,13 +8360,13 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>78</v>
@@ -8383,24 +8375,24 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>128</v>
+        <v>389</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8414,29 +8406,25 @@
         <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>385</v>
+        <v>202</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8460,13 +8448,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8484,31 +8472,31 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>384</v>
+        <v>204</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>393</v>
+        <v>205</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8516,18 +8504,18 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>78</v>
@@ -8539,15 +8527,17 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M54" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8584,31 +8574,31 @@
         <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
@@ -8617,7 +8607,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8626,43 +8616,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8698,19 +8690,19 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8722,16 +8714,16 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8740,9 +8732,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8750,35 +8742,31 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8826,28 +8814,28 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8858,18 +8846,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>78</v>
@@ -8881,15 +8869,17 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M57" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
@@ -8926,31 +8916,31 @@
         <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8959,7 +8949,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8968,43 +8958,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9040,40 +9032,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9082,9 +9074,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9092,13 +9084,13 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9107,20 +9099,18 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9168,7 +9158,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9186,10 +9176,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9198,9 +9188,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9208,13 +9198,13 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9223,18 +9213,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="M60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9258,13 +9248,11 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>399</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9282,7 +9270,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9300,10 +9288,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9314,7 +9302,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9322,7 +9310,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
@@ -9337,17 +9325,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9372,11 +9360,13 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X61" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y61" t="s" s="2">
-        <v>402</v>
+        <v>78</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9394,7 +9384,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9412,10 +9402,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9424,9 +9414,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9440,7 +9430,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9449,17 +9439,19 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M62" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="N62" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9508,7 +9500,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9526,10 +9518,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9540,7 +9532,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9563,19 +9555,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9624,7 +9616,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9642,10 +9634,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9654,9 +9646,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9670,7 +9662,7 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9679,24 +9671,22 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>287</v>
+        <v>404</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9716,13 +9706,13 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
@@ -9740,7 +9730,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>291</v>
+        <v>403</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9755,16 +9745,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>292</v>
+        <v>410</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9772,7 +9762,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9789,27 +9779,31 @@
         <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9830,13 +9824,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9854,7 +9848,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9869,24 +9863,24 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9900,35 +9894,29 @@
         <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P66" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9972,7 +9960,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>416</v>
+        <v>204</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9984,16 +9972,16 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -10015,7 +10003,7 @@
         <v>76</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>78</v>
@@ -10027,13 +10015,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>425</v>
+        <v>131</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -10072,31 +10060,29 @@
         <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB67" s="2"/>
       <c r="AC67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10114,11 +10100,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="C68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10127,10 +10115,10 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10139,13 +10127,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>130</v>
+        <v>426</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>131</v>
+        <v>404</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>132</v>
+        <v>404</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10184,17 +10172,19 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB68" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10203,7 +10193,7 @@
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>136</v>
@@ -10224,13 +10214,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10242,7 +10230,7 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10251,13 +10239,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10308,19 +10296,19 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>213</v>
+        <v>430</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>78</v>
@@ -10340,11 +10328,11 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10360,18 +10348,20 @@
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M70" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10396,13 +10386,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10420,7 +10410,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10432,38 +10422,38 @@
         <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>78</v>
@@ -10475,16 +10465,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10510,13 +10500,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10534,50 +10524,50 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>78</v>
@@ -10589,18 +10579,18 @@
         <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>225</v>
+        <v>453</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="M72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10624,40 +10614,40 @@
         <v>78</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>97</v>
@@ -10666,21 +10656,21 @@
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10688,13 +10678,13 @@
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10703,18 +10693,16 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M73" s="2"/>
-      <c r="N73" t="s" s="2">
-        <v>459</v>
-      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10762,10 +10750,10 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>85</v>
@@ -10777,38 +10765,38 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>78</v>
+        <v>466</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10817,13 +10805,13 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10874,10 +10862,10 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -10889,28 +10877,28 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10929,13 +10917,13 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10986,7 +10974,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -11001,28 +10989,28 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -11041,13 +11029,13 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -11074,13 +11062,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11098,7 +11086,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11113,28 +11101,28 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>488</v>
+        <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>78</v>
+        <v>496</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11144,7 +11132,7 @@
         <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11153,13 +11141,13 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -11186,31 +11174,31 @@
         <v>78</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11225,28 +11213,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>501</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11256,7 +11244,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11265,15 +11253,17 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M78" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11322,7 +11312,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11337,28 +11327,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11377,16 +11367,16 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>510</v>
+        <v>222</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -11412,13 +11402,13 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
@@ -11436,7 +11426,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11451,35 +11441,35 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>518</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>78</v>
@@ -11491,16 +11481,16 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>225</v>
+        <v>529</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -11526,13 +11516,13 @@
         <v>78</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>78</v>
@@ -11550,13 +11540,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11565,38 +11555,38 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AK80" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11605,17 +11595,15 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>532</v>
+        <v>222</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
         <v>78</v>
@@ -11640,13 +11628,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11664,7 +11652,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11679,24 +11667,24 @@
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>536</v>
+        <v>78</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -11710,22 +11698,22 @@
         <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>540</v>
+        <v>202</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>541</v>
+        <v>203</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11752,13 +11740,13 @@
         <v>78</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>78</v>
@@ -11776,19 +11764,19 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>539</v>
+        <v>204</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>78</v>
@@ -11797,10 +11785,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>544</v>
+        <v>205</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11808,18 +11796,18 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>78</v>
@@ -11831,15 +11819,17 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M83" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
         <v>78</v>
@@ -11876,31 +11866,31 @@
         <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>78</v>
@@ -11909,7 +11899,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11918,43 +11908,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11978,31 +11970,29 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="X84" s="2"/>
       <c r="Y84" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -12014,16 +12004,16 @@
         <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -12032,9 +12022,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -12042,35 +12032,31 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12094,11 +12080,13 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X85" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y85" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
@@ -12116,28 +12104,28 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12148,18 +12136,18 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>78</v>
@@ -12171,15 +12159,17 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M86" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
@@ -12216,31 +12206,31 @@
         <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD86" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
@@ -12249,7 +12239,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12258,43 +12248,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12330,40 +12322,40 @@
         <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12372,9 +12364,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12382,13 +12374,13 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12397,20 +12389,18 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12458,7 +12448,7 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12476,10 +12466,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12488,9 +12478,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12498,13 +12488,13 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12513,18 +12503,18 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="M89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12572,7 +12562,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12590,10 +12580,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12604,7 +12594,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12612,7 +12602,7 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>85</v>
@@ -12627,17 +12617,17 @@
         <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12686,7 +12676,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12704,10 +12694,10 @@
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12716,9 +12706,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12732,7 +12722,7 @@
         <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12741,17 +12731,19 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M91" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="N91" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12800,7 +12792,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12818,10 +12810,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12832,7 +12824,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12855,19 +12847,19 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12916,7 +12908,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12934,10 +12926,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12946,9 +12938,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12962,7 +12954,7 @@
         <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12971,20 +12963,16 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>204</v>
+        <v>555</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>287</v>
+        <v>537</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13032,13 +13020,13 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>291</v>
+        <v>554</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -13050,21 +13038,21 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>293</v>
+        <v>557</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -13078,22 +13066,22 @@
         <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>540</v>
+        <v>202</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>559</v>
+        <v>203</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -13144,19 +13132,19 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>557</v>
+        <v>204</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>78</v>
@@ -13165,10 +13153,10 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>560</v>
+        <v>205</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13176,18 +13164,18 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>78</v>
@@ -13199,15 +13187,17 @@
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M95" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13244,31 +13234,31 @@
         <v>78</v>
       </c>
       <c r="AA95" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>78</v>
@@ -13277,7 +13267,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13286,41 +13276,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>210</v>
+        <v>561</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>211</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>186</v>
+        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
@@ -13358,31 +13348,31 @@
         <v>78</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>213</v>
+        <v>564</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>78</v>
@@ -13391,7 +13381,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13400,9 +13390,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13410,13 +13400,13 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -13425,16 +13415,16 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13460,13 +13450,13 @@
         <v>78</v>
       </c>
       <c r="W97" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>78</v>
+        <v>571</v>
       </c>
       <c r="Z97" t="s" s="2">
         <v>78</v>
@@ -13484,7 +13474,7 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13493,7 +13483,7 @@
         <v>85</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>97</v>
@@ -13516,7 +13506,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13539,16 +13529,16 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13574,13 +13564,13 @@
         <v>78</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>573</v>
+        <v>78</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>78</v>
@@ -13598,7 +13588,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13619,7 +13609,7 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13630,7 +13620,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13653,16 +13643,16 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13712,7 +13702,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13733,7 +13723,7 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13742,9 +13732,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13758,7 +13748,7 @@
         <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13767,16 +13757,16 @@
         <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13802,13 +13792,13 @@
         <v>78</v>
       </c>
       <c r="W100" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
+        <v>587</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>588</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -13826,13 +13816,13 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>78</v>
@@ -13841,24 +13831,24 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>128</v>
+        <v>591</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13869,10 +13859,10 @@
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13881,16 +13871,16 @@
         <v>86</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>225</v>
+        <v>594</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13916,13 +13906,13 @@
         <v>78</v>
       </c>
       <c r="W101" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>590</v>
+        <v>78</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="Z101" t="s" s="2">
         <v>78</v>
@@ -13940,7 +13930,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13955,16 +13945,16 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13972,7 +13962,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
@@ -13992,20 +13982,18 @@
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
         <v>78</v>
@@ -14054,7 +14042,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14069,16 +14057,16 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -14086,11 +14074,11 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" t="s" s="2">
-        <v>78</v>
+        <v>609</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14100,7 +14088,7 @@
         <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14109,15 +14097,17 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M103" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
         <v>78</v>
@@ -14154,19 +14144,19 @@
         <v>78</v>
       </c>
       <c r="AA103" t="s" s="2">
-        <v>78</v>
+        <v>614</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>78</v>
+        <v>615</v>
       </c>
       <c r="AC103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14181,35 +14171,37 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AK103" t="s" s="2">
+      <c r="B104" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>86</v>
@@ -14221,16 +14213,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14268,19 +14260,19 @@
         <v>78</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>617</v>
+        <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>618</v>
+        <v>78</v>
       </c>
       <c r="AC104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD104" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14295,13 +14287,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14312,13 +14304,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14337,16 +14329,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14396,7 +14388,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14411,13 +14403,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14428,13 +14420,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14453,16 +14445,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14512,7 +14504,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14527,13 +14519,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14544,13 +14536,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14569,16 +14561,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14628,7 +14620,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14643,13 +14635,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14660,13 +14652,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>628</v>
+        <v>146</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14685,16 +14677,16 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14744,7 +14736,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14759,13 +14751,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14776,13 +14768,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>146</v>
+        <v>628</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14801,16 +14793,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14860,7 +14852,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14875,13 +14867,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14892,13 +14884,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14917,16 +14909,16 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
@@ -14976,7 +14968,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14991,13 +14983,13 @@
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15006,43 +14998,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>633</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J111" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="K111" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="K111" t="s" s="2">
-        <v>614</v>
-      </c>
       <c r="L111" t="s" s="2">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
@@ -15092,7 +15082,7 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
@@ -15107,13 +15097,13 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>619</v>
+        <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -15124,11 +15114,11 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
-        <v>78</v>
+        <v>640</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15147,18 +15137,20 @@
         <v>86</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>636</v>
+        <v>222</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="O112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15182,13 +15174,13 @@
         <v>78</v>
       </c>
       <c r="W112" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
+        <v>645</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>78</v>
+        <v>646</v>
       </c>
       <c r="Z112" t="s" s="2">
         <v>78</v>
@@ -15206,7 +15198,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15224,25 +15216,25 @@
         <v>78</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>78</v>
+        <v>648</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
-        <v>643</v>
+        <v>78</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15258,23 +15250,19 @@
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>225</v>
+        <v>650</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>644</v>
+        <v>47</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>647</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15298,31 +15286,31 @@
         <v>78</v>
       </c>
       <c r="W113" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>648</v>
+        <v>78</v>
       </c>
       <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>76</v>
@@ -15337,24 +15325,24 @@
         <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>78</v>
+        <v>652</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>640</v>
+        <v>451</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
@@ -15365,7 +15353,7 @@
         <v>76</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>78</v>
@@ -15374,16 +15362,16 @@
         <v>78</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>653</v>
+        <v>201</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>47</v>
+        <v>656</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -15434,13 +15422,13 @@
         <v>78</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AF114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>78</v>
@@ -15449,24 +15437,24 @@
         <v>97</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>655</v>
+        <v>78</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>657</v>
+        <v>78</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" t="s" s="2">
@@ -15477,7 +15465,7 @@
         <v>76</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>78</v>
@@ -15486,18 +15474,20 @@
         <v>78</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>204</v>
+        <v>660</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M115" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
         <v>78</v>
@@ -15546,13 +15536,13 @@
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>78</v>
@@ -15561,137 +15551,23 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>78</v>
+        <v>664</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>454</v>
+        <v>128</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="B116" s="2"/>
-      <c r="C116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D116" s="2"/>
-      <c r="E116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P116" s="2"/>
-      <c r="Q116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN116" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN116">
+  <autoFilter ref="A1:AN115">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15701,7 +15577,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI115">
+  <conditionalFormatting sqref="A2:AI114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1596,7 +1596,7 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
 </t>
   </si>
   <si>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$109</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1443,7 +1443,7 @@
     <t>ServiceRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>
@@ -1754,86 +1754,6 @@
     <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
   </si>
   <si>
-    <t>ServiceRequest.locationReference.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
     <t>ServiceRequest.reasonCode</t>
   </si>
   <si>
@@ -1867,7 +1787,7 @@
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ObservationInicioLE)
 </t>
   </si>
   <si>
@@ -1947,7 +1867,7 @@
     <t>.outboundRelationship[typeCode=PERT].target</t>
   </si>
   <si>
-    <t>reserva</t>
+    <t>cita</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/AppointmentInicioLE)
@@ -1955,10 +1875,6 @@
   </si>
   <si>
     <t>paciente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
-</t>
   </si>
   <si>
     <t>Anamnesis</t>
@@ -2407,7 +2323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN115"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -11228,7 +11144,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>505</v>
       </c>
@@ -11244,7 +11160,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -12938,7 +12854,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>554</v>
       </c>
@@ -12951,10 +12867,10 @@
         <v>76</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -13050,7 +12966,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>558</v>
       </c>
@@ -13066,24 +12982,26 @@
         <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>202</v>
+        <v>559</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M94" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>78</v>
@@ -13108,13 +13026,13 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>78</v>
+        <v>562</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
@@ -13132,31 +13050,31 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>204</v>
+        <v>558</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>564</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>205</v>
+        <v>566</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13164,11 +13082,11 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13184,19 +13102,19 @@
         <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>130</v>
+        <v>569</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>207</v>
+        <v>570</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>208</v>
+        <v>571</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>183</v>
+        <v>572</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
@@ -13234,19 +13152,19 @@
         <v>78</v>
       </c>
       <c r="AA95" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>210</v>
+        <v>568</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13258,27 +13176,27 @@
         <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>78</v>
+        <v>573</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>205</v>
+        <v>575</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13286,32 +13204,30 @@
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>201</v>
+        <v>577</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
         <v>78</v>
@@ -13360,28 +13276,28 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>565</v>
+        <v>78</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>581</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>128</v>
+        <v>582</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13392,39 +13308,39 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>99</v>
+        <v>585</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13450,37 +13366,37 @@
         <v>78</v>
       </c>
       <c r="W97" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>570</v>
+        <v>78</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="Z97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>78</v>
@@ -13489,13 +13405,13 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>128</v>
+        <v>593</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13504,13 +13420,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B98" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="C98" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13520,25 +13438,25 @@
         <v>85</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>188</v>
+        <v>595</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13588,13 +13506,13 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>78</v>
@@ -13603,13 +13521,13 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>196</v>
+        <v>593</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13618,13 +13536,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="B99" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="C99" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13634,25 +13554,25 @@
         <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>201</v>
+        <v>585</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13702,13 +13622,13 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>78</v>
@@ -13717,13 +13637,13 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>128</v>
+        <v>593</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13736,9 +13656,11 @@
       <c r="A100" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="B100" s="2"/>
+      <c r="B100" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="C100" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13754,19 +13676,19 @@
         <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>222</v>
+        <v>598</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13792,13 +13714,13 @@
         <v>78</v>
       </c>
       <c r="W100" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>588</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -13831,56 +13753,58 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B101" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="C101" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13930,7 +13854,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13945,38 +13869,40 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B102" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C102" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13985,15 +13911,17 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M102" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
         <v>78</v>
@@ -14042,7 +13970,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14057,13 +13985,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14072,20 +14000,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B103" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="C103" t="s" s="2">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>86</v>
@@ -14097,16 +14027,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14144,19 +14074,19 @@
         <v>78</v>
       </c>
       <c r="AA103" t="s" s="2">
-        <v>614</v>
+        <v>78</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>615</v>
+        <v>78</v>
       </c>
       <c r="AC103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14171,13 +14101,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14188,13 +14118,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14213,16 +14143,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14272,7 +14202,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14287,13 +14217,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14302,43 +14232,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="B105" s="2"/>
       <c r="C105" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J105" t="s" s="2">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14388,7 +14316,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14403,13 +14331,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14418,45 +14346,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="B106" s="2"/>
       <c r="C106" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I106" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J106" t="s" s="2">
-        <v>624</v>
+        <v>222</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14480,13 +14408,13 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>78</v>
+        <v>620</v>
       </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
@@ -14504,7 +14432,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14519,40 +14447,38 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>78</v>
+        <v>622</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="B107" s="2"/>
       <c r="C107" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14561,17 +14487,15 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>611</v>
+        <v>47</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
         <v>78</v>
@@ -14620,7 +14544,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14635,30 +14559,28 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>617</v>
+        <v>451</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>78</v>
+        <v>628</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="B108" s="2"/>
       <c r="C108" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14668,26 +14590,24 @@
         <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J108" t="s" s="2">
-        <v>627</v>
+        <v>201</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
         <v>78</v>
@@ -14736,13 +14656,13 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -14751,13 +14671,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>617</v>
+        <v>451</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14766,25 +14686,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14793,16 +14711,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14852,7 +14770,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14867,707 +14785,23 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>617</v>
+        <v>128</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="D110" s="2"/>
-      <c r="E110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F110" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P110" s="2"/>
-      <c r="Q110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B111" s="2"/>
-      <c r="C111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D111" s="2"/>
-      <c r="E111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P111" s="2"/>
-      <c r="Q111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B112" s="2"/>
-      <c r="C112" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="D112" s="2"/>
-      <c r="E112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P112" s="2"/>
-      <c r="Q112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D113" s="2"/>
-      <c r="E113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P113" s="2"/>
-      <c r="Q113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B114" s="2"/>
-      <c r="C114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D114" s="2"/>
-      <c r="E114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P114" s="2"/>
-      <c r="Q114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B115" s="2"/>
-      <c r="C115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D115" s="2"/>
-      <c r="E115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P115" s="2"/>
-      <c r="Q115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN115" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN115">
+  <autoFilter ref="A1:AN109">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15577,7 +14811,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI114">
+  <conditionalFormatting sqref="A2:AI108">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t>Fundamente de la Priorización</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
     <t>EstadoInterconsultaCodigo</t>
@@ -4339,7 +4342,7 @@
         <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -4411,7 +4414,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4425,7 +4428,7 @@
         <v>129</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>78</v>
@@ -4447,13 +4450,13 @@
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -4539,7 +4542,7 @@
         <v>129</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>78</v>
@@ -4561,13 +4564,13 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -4653,7 +4656,7 @@
         <v>129</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>78</v>
@@ -4675,13 +4678,13 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -4767,7 +4770,7 @@
         <v>129</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>78</v>
@@ -4789,13 +4792,13 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -4878,11 +4881,11 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4904,16 +4907,16 @@
         <v>130</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O23" t="s" s="2">
         <v>78</v>
@@ -4962,7 +4965,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -4994,7 +4997,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -5005,7 +5008,7 @@
         <v>85</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>86</v>
@@ -5017,16 +5020,16 @@
         <v>86</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
@@ -5064,10 +5067,10 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
@@ -5076,7 +5079,7 @@
         <v>134</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5091,27 +5094,27 @@
         <v>97</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>78</v>
@@ -5133,16 +5136,16 @@
         <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -5192,7 +5195,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5207,24 +5210,24 @@
         <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5247,13 +5250,13 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -5304,7 +5307,7 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
@@ -5325,7 +5328,7 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5336,11 +5339,11 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -5362,13 +5365,13 @@
         <v>130</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -5409,7 +5412,7 @@
         <v>133</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
@@ -5418,7 +5421,7 @@
         <v>134</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
@@ -5439,7 +5442,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5450,7 +5453,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5476,16 +5479,16 @@
         <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
@@ -5510,13 +5513,13 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
@@ -5534,7 +5537,7 @@
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
@@ -5555,7 +5558,7 @@
         <v>128</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5566,7 +5569,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5589,19 +5592,19 @@
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5626,13 +5629,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5650,7 +5653,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5668,10 +5671,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5682,7 +5685,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5705,13 +5708,13 @@
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5762,7 +5765,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5783,7 +5786,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5794,11 +5797,11 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5820,13 +5823,13 @@
         <v>130</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -5867,7 +5870,7 @@
         <v>133</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
@@ -5876,7 +5879,7 @@
         <v>134</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
@@ -5897,7 +5900,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5908,7 +5911,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5931,19 +5934,19 @@
         <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>78</v>
@@ -5992,7 +5995,7 @@
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6010,10 +6013,10 @@
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6024,7 +6027,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6047,13 +6050,13 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -6104,7 +6107,7 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
@@ -6125,7 +6128,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6136,11 +6139,11 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6162,13 +6165,13 @@
         <v>130</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
@@ -6209,7 +6212,7 @@
         <v>133</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
@@ -6218,7 +6221,7 @@
         <v>134</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
@@ -6239,7 +6242,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6250,7 +6253,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6276,16 +6279,16 @@
         <v>99</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>78</v>
@@ -6334,7 +6337,7 @@
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
@@ -6352,10 +6355,10 @@
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6366,7 +6369,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6389,16 +6392,16 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
@@ -6448,7 +6451,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6466,10 +6469,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6480,7 +6483,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6506,14 +6509,14 @@
         <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
@@ -6523,7 +6526,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6562,7 +6565,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6580,10 +6583,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6594,7 +6597,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6617,17 +6620,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6676,7 +6679,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6694,10 +6697,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6708,7 +6711,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6731,19 +6734,19 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6792,7 +6795,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6810,10 +6813,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6824,7 +6827,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6847,19 +6850,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6911,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6926,10 +6929,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6940,7 +6943,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6966,16 +6969,16 @@
         <v>99</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -6988,7 +6991,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7024,7 +7027,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7042,10 +7045,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7056,7 +7059,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7079,16 +7082,16 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -7102,7 +7105,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7138,7 +7141,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7156,10 +7159,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7170,7 +7173,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7193,13 +7196,13 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -7250,7 +7253,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7268,10 +7271,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7282,7 +7285,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7305,16 +7308,16 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
@@ -7364,7 +7367,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7382,10 +7385,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7396,7 +7399,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7419,16 +7422,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7478,7 +7481,7 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
@@ -7493,13 +7496,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7510,7 +7513,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7536,13 +7539,13 @@
         <v>99</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7592,7 +7595,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7607,13 +7610,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7624,11 +7627,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7647,13 +7650,13 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7704,7 +7707,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7719,13 +7722,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7736,11 +7739,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7759,13 +7762,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7816,7 +7819,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7831,13 +7834,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7848,11 +7851,11 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7871,19 +7874,19 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>78</v>
@@ -7932,7 +7935,7 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
@@ -7947,13 +7950,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7964,7 +7967,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7990,13 +7993,13 @@
         <v>105</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -8022,13 +8025,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8046,7 +8049,7 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>85</v>
@@ -8061,24 +8064,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8104,13 +8107,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8136,13 +8139,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8160,7 +8163,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8175,16 +8178,16 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8192,7 +8195,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8215,19 +8218,19 @@
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -8252,13 +8255,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8276,7 +8279,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>76</v>
@@ -8294,13 +8297,13 @@
         <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8308,7 +8311,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8331,13 +8334,13 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -8388,7 +8391,7 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
@@ -8409,7 +8412,7 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8420,11 +8423,11 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8446,13 +8449,13 @@
         <v>130</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -8493,7 +8496,7 @@
         <v>133</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
@@ -8502,7 +8505,7 @@
         <v>134</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
@@ -8523,7 +8526,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8534,7 +8537,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8557,19 +8560,19 @@
         <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>78</v>
@@ -8618,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8636,10 +8639,10 @@
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8650,7 +8653,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8673,13 +8676,13 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -8730,7 +8733,7 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
@@ -8751,7 +8754,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8762,11 +8765,11 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8788,13 +8791,13 @@
         <v>130</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
@@ -8835,7 +8838,7 @@
         <v>133</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
@@ -8844,7 +8847,7 @@
         <v>134</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8865,7 +8868,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8876,7 +8879,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8902,16 +8905,16 @@
         <v>99</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
@@ -8960,7 +8963,7 @@
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
@@ -8978,10 +8981,10 @@
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8992,7 +8995,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9015,16 +9018,16 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -9074,7 +9077,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9092,10 +9095,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9106,7 +9109,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9132,14 +9135,14 @@
         <v>105</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
@@ -9164,11 +9167,11 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9186,7 +9189,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9204,10 +9207,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9218,7 +9221,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9241,17 +9244,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9300,7 +9303,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9318,10 +9321,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9332,7 +9335,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9355,19 +9358,19 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9416,7 +9419,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9434,10 +9437,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9448,7 +9451,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9471,19 +9474,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9532,7 +9535,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9550,10 +9553,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9564,7 +9567,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9590,10 +9593,10 @@
         <v>105</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -9601,7 +9604,7 @@
         <v>78</v>
       </c>
       <c r="P64" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q64" t="s" s="2">
         <v>78</v>
@@ -9622,13 +9625,13 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
@@ -9646,7 +9649,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9661,16 +9664,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9678,7 +9681,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9701,70 +9704,70 @@
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9779,13 +9782,13 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9796,7 +9799,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9819,13 +9822,13 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9876,7 +9879,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9908,7 +9911,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9986,7 +9989,7 @@
         <v>134</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
@@ -10018,10 +10021,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>78</v>
@@ -10043,13 +10046,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10100,7 +10103,7 @@
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10132,7 +10135,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -10155,13 +10158,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10212,7 +10215,7 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
@@ -10244,11 +10247,11 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10267,16 +10270,16 @@
         <v>86</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -10302,13 +10305,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10326,7 +10329,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10341,28 +10344,28 @@
         <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10381,16 +10384,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10416,13 +10419,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10440,7 +10443,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10449,7 +10452,7 @@
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>97</v>
@@ -10458,21 +10461,21 @@
         <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10495,17 +10498,17 @@
         <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>78</v>
@@ -10554,7 +10557,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10572,10 +10575,10 @@
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10586,7 +10589,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10609,13 +10612,13 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -10666,7 +10669,7 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>85</v>
@@ -10681,28 +10684,28 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10721,13 +10724,13 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10778,7 +10781,7 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
@@ -10793,28 +10796,28 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10833,13 +10836,13 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10890,7 +10893,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10905,24 +10908,24 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10945,13 +10948,13 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -10978,13 +10981,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11002,7 +11005,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11023,22 +11026,22 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11057,13 +11060,13 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -11114,7 +11117,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11129,28 +11132,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11169,16 +11172,16 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
@@ -11228,7 +11231,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11243,28 +11246,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11283,16 +11286,16 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -11318,13 +11321,13 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
@@ -11342,7 +11345,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11357,16 +11360,16 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11374,11 +11377,11 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11397,16 +11400,16 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -11456,7 +11459,7 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
@@ -11471,16 +11474,16 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11488,7 +11491,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11511,13 +11514,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11544,13 +11547,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11568,7 +11571,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11589,10 +11592,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11600,7 +11603,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -11623,13 +11626,13 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11680,7 +11683,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11701,7 +11704,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11712,11 +11715,11 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11738,13 +11741,13 @@
         <v>130</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11785,7 +11788,7 @@
         <v>133</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
@@ -11794,7 +11797,7 @@
         <v>134</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
@@ -11815,7 +11818,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11826,7 +11829,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11849,19 +11852,19 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>78</v>
@@ -11886,11 +11889,11 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X84" s="2"/>
       <c r="Y84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11908,7 +11911,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -11926,10 +11929,10 @@
         <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11940,7 +11943,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11963,13 +11966,13 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -12020,7 +12023,7 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
@@ -12041,7 +12044,7 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12052,11 +12055,11 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -12078,13 +12081,13 @@
         <v>130</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
@@ -12125,7 +12128,7 @@
         <v>133</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
@@ -12134,7 +12137,7 @@
         <v>134</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12155,7 +12158,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12166,7 +12169,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -12192,16 +12195,16 @@
         <v>99</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>78</v>
@@ -12250,7 +12253,7 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
@@ -12268,10 +12271,10 @@
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12282,7 +12285,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12305,16 +12308,16 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
@@ -12364,7 +12367,7 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12382,10 +12385,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12396,7 +12399,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12422,14 +12425,14 @@
         <v>105</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
@@ -12478,7 +12481,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12496,10 +12499,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12510,7 +12513,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12533,17 +12536,17 @@
         <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12592,7 +12595,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12610,10 +12613,10 @@
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12624,7 +12627,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12647,19 +12650,19 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12708,7 +12711,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12726,10 +12729,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12740,7 +12743,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12763,19 +12766,19 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12824,7 +12827,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12842,10 +12845,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12856,7 +12859,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12879,13 +12882,13 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -12936,7 +12939,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -12957,10 +12960,10 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12968,7 +12971,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12991,16 +12994,16 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
@@ -13026,13 +13029,13 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
@@ -13050,7 +13053,7 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13065,16 +13068,16 @@
         <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13082,7 +13085,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13105,16 +13108,16 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
@@ -13164,7 +13167,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13179,16 +13182,16 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13196,7 +13199,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13219,13 +13222,13 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -13276,7 +13279,7 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
@@ -13291,13 +13294,13 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13308,11 +13311,11 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13331,16 +13334,16 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13378,10 +13381,10 @@
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
@@ -13390,7 +13393,7 @@
         <v>134</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13405,13 +13408,13 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13422,13 +13425,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13447,16 +13450,16 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13506,7 +13509,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13521,13 +13524,13 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13538,13 +13541,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13563,16 +13566,16 @@
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13622,7 +13625,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13637,13 +13640,13 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13654,13 +13657,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13679,16 +13682,16 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13738,7 +13741,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13753,13 +13756,13 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13770,13 +13773,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13795,16 +13798,16 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13854,7 +13857,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13869,13 +13872,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13886,13 +13889,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>146</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13911,16 +13914,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13970,7 +13973,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -13985,13 +13988,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14002,13 +14005,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14027,16 +14030,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14086,7 +14089,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14101,13 +14104,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14118,13 +14121,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14143,16 +14146,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14202,7 +14205,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14217,13 +14220,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14234,7 +14237,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" t="s" s="2">
@@ -14257,16 +14260,16 @@
         <v>86</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14316,7 +14319,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14334,10 +14337,10 @@
         <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14348,11 +14351,11 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14371,19 +14374,19 @@
         <v>86</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>78</v>
@@ -14408,13 +14411,13 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
@@ -14432,7 +14435,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14450,21 +14453,21 @@
         <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" t="s" s="2">
@@ -14487,13 +14490,13 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -14544,7 +14547,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14559,24 +14562,24 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" t="s" s="2">
@@ -14599,13 +14602,13 @@
         <v>86</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -14656,7 +14659,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14674,10 +14677,10 @@
         <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14688,7 +14691,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
@@ -14711,16 +14714,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14770,7 +14773,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14785,13 +14788,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
